--- a/ExcelFiles/stats-ventes.xlsx
+++ b/ExcelFiles/stats-ventes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,10 +466,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1752858996</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1752858996</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -497,10 +495,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1752858996</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1752858996</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -528,10 +524,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1752858996</t>
-        </is>
+      <c r="A4" t="n">
+        <v>1752858996</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -559,10 +553,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1752858996</t>
-        </is>
+      <c r="A5" t="n">
+        <v>1752858996</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -587,6 +579,95 @@
       </c>
       <c r="G5" t="n">
         <v>1800</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1752950310</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-07-19 19:39:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>P0218</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bouteille d'eau</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>600</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1752951038</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-07-19 19:51:21</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>UC i5</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F7" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2000000000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1752951136</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-07-19 19:53:12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>UC i5</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G8" t="n">
+        <v>200000000</v>
       </c>
     </row>
   </sheetData>
